--- a/Utilities/Powershell Utilities/TestFileCache/BLANK_BOE_Receivable.xlsx
+++ b/Utilities/Powershell Utilities/TestFileCache/BLANK_BOE_Receivable.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -8,22 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\williamt\source\skillsinc\skills-inc-org\SQL-Projects\Utilities\Powershell Utilities\TestFileCache\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{93007996-95C2-49ED-8975-D358F37EE952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C43EEE-E6C5-4F1A-B3D5-E0C45F26C5EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Detail Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -76,7 +69,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -144,7 +137,7 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -416,7 +409,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
